--- a/BASE DE CONTAGEM.xlsx
+++ b/BASE DE CONTAGEM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\otavi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A1E680-5D67-463F-986D-AD24EEE83375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540AAFF7-CD4F-41E3-9097-8C462B8A7595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2927615E-0AE4-4797-9F7D-0E39B943AA17}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="cod prod" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'base '!$A$1:$F$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'base '!$A$1:$F$216</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2985" uniqueCount="2749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="2752">
   <si>
     <t>Reduzido</t>
   </si>
@@ -8290,6 +8290,15 @@
   </si>
   <si>
     <t>prod</t>
+  </si>
+  <si>
+    <t>FANTA UVA ZERO LT 350</t>
+  </si>
+  <si>
+    <t>CRYSTAL LIM PET 510ML</t>
+  </si>
+  <si>
+    <t>CRYSTAL MAR PET 510ML</t>
   </si>
 </sst>
 </file>
@@ -8750,7 +8759,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -12770,6 +12779,66 @@
         <v>76</v>
       </c>
     </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>1000271</v>
+      </c>
+      <c r="B214">
+        <v>1000271</v>
+      </c>
+      <c r="C214" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D214" s="1">
+        <v>6</v>
+      </c>
+      <c r="E214" s="1">
+        <v>540</v>
+      </c>
+      <c r="F214" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>1001746</v>
+      </c>
+      <c r="B215">
+        <v>1001746</v>
+      </c>
+      <c r="C215" t="s">
+        <v>2750</v>
+      </c>
+      <c r="D215" s="1">
+        <v>12</v>
+      </c>
+      <c r="E215" s="1">
+        <v>196</v>
+      </c>
+      <c r="F215" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>1001747</v>
+      </c>
+      <c r="B216">
+        <v>1001747</v>
+      </c>
+      <c r="C216" t="s">
+        <v>2751</v>
+      </c>
+      <c r="D216" s="1">
+        <v>12</v>
+      </c>
+      <c r="E216" s="1">
+        <v>196</v>
+      </c>
+      <c r="F216" s="1">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12777,7 +12846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B050F3-94A5-49B8-BEBC-15FF6778D174}">
-  <dimension ref="A1:B2765"/>
+  <dimension ref="A1:B2769"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -34902,6 +34971,38 @@
       </c>
       <c r="B2765" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2766">
+        <v>1000306</v>
+      </c>
+      <c r="B2766" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2767">
+        <v>1000271</v>
+      </c>
+      <c r="B2767" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2768">
+        <v>1001746</v>
+      </c>
+      <c r="B2768" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2769">
+        <v>1001747</v>
+      </c>
+      <c r="B2769" t="s">
+        <v>2751</v>
       </c>
     </row>
   </sheetData>
